--- a/БД СПС.xlsx
+++ b/БД СПС.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rosla\Documents\GitHub\swx_neiro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73FF44E5-8111-496B-A5A2-FAAC52E16099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB6A3B9-09F5-45EA-BA9D-37109396663C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41172" yWindow="4128" windowWidth="13176" windowHeight="22656" xr2:uid="{94138313-3E12-4D24-A433-C6E5B490A5A8}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="14020" activeTab="1" xr2:uid="{94138313-3E12-4D24-A433-C6E5B490A5A8}"/>
   </bookViews>
   <sheets>
     <sheet name="ОБЩАЯ БД" sheetId="1" r:id="rId1"/>
@@ -17231,14 +17231,13 @@
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.81640625" customWidth="1"/>
-    <col min="2" max="2" width="6.7265625" customWidth="1"/>
-    <col min="3" max="3" width="7.81640625" customWidth="1"/>
-    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.1796875" customWidth="1"/>
+    <col min="8" max="8" width="5.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
